--- a/src/main/resources/templates/xlsx/2차전형점수양식.xlsx
+++ b/src/main/resources/templates/xlsx/2차전형점수양식.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gimhanul/maru/src/main/resources/templates/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/main/resources/templates/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AF3A13-86E5-3143-842F-C91B7E8A3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCC475E-E729-AF4B-9970-66EFC1E26B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17800" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>수험번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,19 +50,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>심층면접</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코딩 테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>응시 여부</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NCS</t>
+    <t>자기주도학습영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인성영역</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -169,9 +165,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -209,7 +205,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -315,7 +311,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -457,7 +453,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -465,19 +461,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8EB960-16E4-4546-BE22-CABF45F1D2EB}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" customHeight="1">
+    <row r="1" spans="1:6" ht="29" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,16 +483,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/templates/xlsx/2차전형점수양식.xlsx
+++ b/src/main/resources/templates/xlsx/2차전형점수양식.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/main/resources/templates/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCC475E-E729-AF4B-9970-66EFC1E26B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648D0240-F72D-B246-85C7-463D1FE4836F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
@@ -38,10 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>수험번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -59,6 +55,10 @@
   </si>
   <si>
     <t>인성영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>면접번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -474,22 +474,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="29" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
